--- a/media_master.xlsx
+++ b/media_master.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haneenalbosta/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076E6735-18A7-D242-BFEA-496250CF7C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>Media ID</t>
   </si>
@@ -62,18 +68,6 @@
   </si>
   <si>
     <t>MED-0005</t>
-  </si>
-  <si>
-    <t>Tryptone soya agar</t>
-  </si>
-  <si>
-    <t>Sabouraud dextrose agar</t>
-  </si>
-  <si>
-    <t>Tryptone soya broth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thioglycolate  medium </t>
   </si>
   <si>
     <t>6245579</t>
@@ -112,12 +106,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,13 +176,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -226,7 +228,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -260,6 +262,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -294,9 +297,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,11 +473,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,24 +512,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>6140313</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>500</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G2" s="2">
         <v>47330</v>
@@ -540,27 +544,27 @@
         <v>1000</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>121824502</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>500</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G3" s="2">
         <v>47118</v>
@@ -575,27 +579,27 @@
         <v>1000</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>6224173</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>500</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4" s="2">
         <v>47542</v>
@@ -610,27 +614,27 @@
         <v>1000</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>3721617</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>500</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G5" s="2">
         <v>47026</v>
@@ -645,27 +649,27 @@
         <v>500</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>500</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>47026</v>
@@ -680,7 +684,7 @@
         <v>1000</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
